--- a/output/金源/无锡金源半导体研究_数据来源与取数清单.xlsx
+++ b/output/金源/无锡金源半导体研究_数据来源与取数清单.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_说明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_已有的行业数据" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_需要从Wind补取" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_待回源或不使用" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_本轮新增来源" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_待回源或不使用" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -60,6 +61,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D6E9D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -115,6 +121,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1240,7 +1249,7 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>托伦斯(301583.SZ)、臻宝科技(688797.SH)、珂玛科技(301611.SZ)、富创精密(688409.SH)、先锋精科、神工股份(688233.SH)、盾源聚芯、凯德石英、唯万密封(301161.SZ)：2022—2025年营业收入、归母净利润、销售毛利率、研发费用及占比、存货周转率、应收账款周转率</t>
+          <t>托伦斯(301583.SZ)、臻宝科技(688797.SH)、珂玛科技(301611.SZ)、富创精密(688409.SH)、先锋精科、神工股份(688233.SH)、盾源聚芯、凯德石英、唯万密封(301161.SZ)：2022—2025年营业收入、归母净利润、销售毛利率、研发费用及占比、存货周转率、应收账款周转率。其中2025年营业收入与归母净利润已从各公司年度报告取得，见表9；仍需Wind补取的是周转率类指标与2022—2024年时间序列</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -1250,7 +1259,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>需Wind</t>
+          <t>部分已有</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1284,7 @@
           <t>第五章、第七章</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>需Wind</t>
         </is>
@@ -1302,7 +1311,7 @@
           <t>第五章</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>需Wind</t>
         </is>
@@ -1329,7 +1338,7 @@
           <t>第三章</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>需Wind</t>
         </is>
@@ -1356,7 +1365,7 @@
           <t>第三章需求端</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>需Wind</t>
         </is>
@@ -1383,7 +1392,7 @@
           <t>第四章密封件路线</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>需Wind</t>
         </is>
@@ -1398,6 +1407,278 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>三、本轮新增取得的原始文件与数据（对应表9、表10、第七章、第八章）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>来源文件或数据</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>发布方</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>取得内容</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>用于哪一处</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>神工股份8-1-1 发行人及保荐机构回复意见（2019年半年报财务数据更新版）</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>发行人与国泰君安证券</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>首轮审核问询函回复，共49个问题</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>表11、表12、图6、7.1—7.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>神工股份8-1-2 关于第二轮审核问询函的回复意见（2019年半年报财务数据更新版）</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>发行人与国泰君安证券</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>第二轮20个问题及其标题</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>表12、图6、7.3—7.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>神工股份8-1 关于第三轮审核问询函的回复意见</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>发行人与国泰君安证券</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>第三轮8个问题，含产量与销量差异、单位能耗、发行人产品</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>表12、图6、7.3、7.4、7.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>神工股份8-1 关于第四轮审核问询函的回复意见</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>发行人与国泰君安证券</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>第四轮8个问题，含两套口径产销比数据、单位设备用水用电量、境外销售单证要求</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>表12、图6、7.7、7.8、7.10、7.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>神工股份8-1 关于上市委审议意见落实函的回复意见</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>发行人与国泰君安证券</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>落实函2个问题，均为非专利技术来源与合作研发模式；保荐机构六项核查程序</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>表12、图6、7.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>神工股份科创板首次公开发行股票招股说明书（注册稿）</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>发行人</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>保荐人为国泰君安证券；募投项目拟投入募集资金总额110,200.22万元；报告期综合毛利率43.73%、55.10%、63.77%、67.25%</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>表9、表14、7.3、8.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>各公司2025年年度报告及年度报告摘要</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>各上市公司</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>表9所列20家企业的2025年营业收入、归母净利润及同比变动</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>表9、5.1、5.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>臻宝科技招股说明书（注册稿）“行业内主要企业”</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>发行人</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>境内外零部件与表面处理企业名单及业务描述，含证券代码</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>表10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>托伦斯招股说明书（注册稿）“行业内主要企业”</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>发行人</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Ferrotec、京鼎精密、超科林、富创精密、先锋精科、珂玛科技、臻宝科技的业务描述</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>表10、4.1、5.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>国泰海通证券关于宁波江丰电子2025年度向特定对象发行A股股票之上市保荐书</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>国泰海通证券</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>保荐人身份、募集资金总额不超过192,782.90万元、募投项目构成</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1415,7 +1696,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>三、目前只有转述出处的内容（写入正文前须回源，回不了则不写）</t>
+          <t>四、目前只有转述出处的内容（写入正文前须回源，回不了则不写）</t>
         </is>
       </c>
     </row>

--- a/output/金源/无锡金源半导体研究_数据来源与取数清单.xlsx
+++ b/output/金源/无锡金源半导体研究_数据来源与取数清单.xlsx
@@ -552,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>（招股书列示，机构待核）</t>
+          <t>Maximize Market Research</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>已有（机构名需回源）</t>
+          <t>已有</t>
         </is>
       </c>
     </row>
@@ -1026,17 +1026,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>约14.28亿美元；预计2030年达21.56亿美元</t>
+          <t>约14.28亿美元；预计2030年达21.56亿美元；2024—2030年CAGR 6.2%</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2023年</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>（招股书列示，机构待核）</t>
+          <t>QY Research</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1046,29 +1046,29 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>已有（机构名需回源）</t>
+          <t>已有</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>陶瓷零部件更换周期</t>
+          <t>全球刻蚀设备用气体分配盘市场规模</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>陶瓷筒、陶瓷板等约1—3年更换一次</t>
+          <t>9.44亿美元（含硅、金属、碳化硅材质）；预计2030年达15.44亿美元，CAGR 7.0%</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2023年</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>QY Research（QYR）</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1085,12 +1085,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>零部件耗材属性分类</t>
+          <t>陶瓷零部件更换周期</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>金属工艺零部件需定期更换但周期较长、可表面处理后再用；金属结构零部件伴随设备生命周期几乎不更换；硅、石英、碳化硅在刻蚀设备中用量大且更换周期较短</t>
+          <t>陶瓷筒、陶瓷板等约1—3年更换一次</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1117,17 +1117,17 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>分产品毛利率基准</t>
+          <t>零部件耗材属性分类</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>匀气盘27.44%、气体分布盘20.05%、加热器14.39%、内衬44.96%、腔体21.35%、冷盘70.89%、静电卡盘基体30.77%</t>
+          <t>金属工艺零部件需定期更换但周期较长、可表面处理后再用；金属结构零部件伴随设备生命周期几乎不更换；硅、石英、碳化硅在刻蚀设备中用量大且更换周期较短</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>2023年</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>托伦斯第二轮审核问询函回复</t>
+          <t>臻宝科技招股说明书（注册稿）</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -1149,30 +1149,62 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t>分产品毛利率基准</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>匀气盘27.44%、气体分布盘20.05%、加热器14.39%、内衬44.96%、腔体21.35%、冷盘70.89%、静电卡盘基体30.77%</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>2023年</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>托伦斯第二轮审核问询函回复</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>已有</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t>行业增速</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>中微公司刻蚀设备产量同比增长231.15%；先锋精科半导体设备零部件收入增速134.64%；珂玛科技半导体领域收入增速205.89%；富创精密半导体设备零部件收入增速55.59%</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>2024年</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>各公司披露</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>托伦斯审核中心意见落实函回复</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>已有</t>
         </is>
@@ -1412,7 +1444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1667,6 +1699,28 @@
       <c r="D12" s="5" t="inlineStr">
         <is>
           <t>8.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>各公司首次公开发行的招股说明书、上市保荐书、发行公告与网上路演公告</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>各发行人与保荐机构</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>表9所列各公司首次公开发行的保荐机构与上市日期。其中正帆科技首次公开发行的保荐机构（主承销商）为国泰君安证券，据其2020年8月7日投资风险特别公告</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>表9、表14、8.2</t>
         </is>
       </c>
     </row>

--- a/output/金源/无锡金源半导体研究_数据来源与取数清单.xlsx
+++ b/output/金源/无锡金源半导体研究_数据来源与取数清单.xlsx
@@ -1444,7 +1444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1456,7 +1456,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>三、本轮新增取得的原始文件与数据（对应表9、表10、第七章、第八章）</t>
+          <t>三、本轮新增取得的原始文件与数据（对应表9、表10、表13、第七章至第九章）</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>表9、表14、7.3、8.2</t>
+          <t>表9、表15、7.3、8.2</t>
         </is>
       </c>
     </row>
@@ -1705,22 +1705,88 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>五家样本企业问询回复中的“中介机构核查程序”章节</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>各发行人与保荐机构、申报会计师、发行人律师</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>按关注点归并的核查材料清单：臻宝科技成本及毛利率9项、收入4项、募投项目6项；托伦斯技术先进性7项、业绩稳定性6项；珂玛科技毛利率3项；神工股份无实际控制人5项、关联关系7项、产销勾稽7项、能耗与境外销售5项、技术来源6项</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>表13、7.3—7.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>无锡金源工商查询平台公示信息（天眼查、企查查）</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>公开工商信息平台</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>统一社会信用代码、成立日期、注册资本与实缴资本、法定代表人、参保人数、企业规模、资质标签、融资轮次标注为B轮。国标行业分类两平台标注不一致，本报告并列列示</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>9.1、9.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>行业媒体关于无锡金源B轮融资的报道</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>投资家网，2025年5月29日</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>融资用途为全氟密封圈、金属喷头等关键配件的研发扩产与工艺优化。同篇提及的专利23项、2024年主营收入增速超60%、年产30万套密封组件为单一来源，未获独立印证，本报告正文未采用，列入表18待核实</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>9.1、表18</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
           <t>各公司首次公开发行的招股说明书、上市保荐书、发行公告与网上路演公告</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>各发行人与保荐机构</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>表9所列各公司首次公开发行的保荐机构与上市日期。其中正帆科技首次公开发行的保荐机构（主承销商）为国泰君安证券，据其2020年8月7日投资风险特别公告</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>表9、表14、8.2</t>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>表9、表15、8.2</t>
         </is>
       </c>
     </row>

--- a/output/金源/无锡金源半导体研究_数据来源与取数清单.xlsx
+++ b/output/金源/无锡金源半导体研究_数据来源与取数清单.xlsx
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>按关注点归并的核查材料清单：臻宝科技成本及毛利率9项、收入4项、募投项目6项；托伦斯技术先进性7项、业绩稳定性6项；珂玛科技毛利率3项；神工股份无实际控制人5项、关联关系7项、产销勾稽7项、能耗与境外销售5项、技术来源6项</t>
+          <t>按关注点归并的核查材料清单：臻宝科技成本及毛利率9项、收入4项、募投项目8项，另就募投项目场地安排单列7项；托伦斯技术先进性7项、业绩稳定性6项；珂玛科技毛利率3项；神工股份无实际控制人5项、关联关系7项、产销勾稽7项、能耗与境外销售5项、技术来源6项</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">

--- a/output/金源/无锡金源半导体研究_数据来源与取数清单.xlsx
+++ b/output/金源/无锡金源半导体研究_数据来源与取数清单.xlsx
@@ -1281,12 +1281,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>托伦斯(301583.SZ)、臻宝科技(688797.SH)、珂玛科技(301611.SZ)、富创精密(688409.SH)、先锋精科、神工股份(688233.SH)、盾源聚芯、凯德石英、唯万密封(301161.SZ)：2022—2025年营业收入、归母净利润、销售毛利率、研发费用及占比、存货周转率、应收账款周转率。其中2025年营业收入与归母净利润已从各公司年度报告取得，见表9；仍需Wind补取的是周转率类指标与2022—2024年时间序列</t>
+          <t>托伦斯(301583.SZ)、臻宝科技(688797.SH)、珂玛科技(301611.SZ)、富创精密(688409.SH)、先锋精科、神工股份(688233.SH)、盾源聚芯、凯德石英、唯万密封(301161.SZ)：2022—2025年营业收入、归母净利润、销售毛利率、研发费用及占比、存货周转率、应收账款周转率。其中2025年营业收入与归母净利润已从各公司年度报告取得，见表8；仍需Wind补取的是周转率类指标与2022—2024年时间序列</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>第四章竞争格局、第五章可比公司对照</t>
+          <t>第五章可比公司</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>第五章、第七章</t>
+          <t>第五章、第六章</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>第三章</t>
+          <t>第四章</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>第三章需求端</t>
+          <t>第四章需求端</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>第四章密封件路线</t>
+          <t>第五章密封件路线</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -1456,7 +1456,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>三、本轮新增取得的原始文件与数据（对应表9、表10、表13、第七章至第九章）</t>
+          <t>三、本轮新增取得的原始文件与数据（对应表1至表16、第五章至第七章）</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>表11、表12、图6、7.1—7.11</t>
+          <t>表12、图4、6.1—6.7</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>表12、图6、7.3—7.11</t>
+          <t>表12、图4、6.2—6.7</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>表12、图6、7.3、7.4、7.8</t>
+          <t>表12、图4、6.2、6.3、6.6</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>表12、图6、7.7、7.8、7.10、7.11</t>
+          <t>表12、图4、6.5、6.6</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>表12、图6、7.5</t>
+          <t>表12、图4</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>表9、表15、7.3、8.2</t>
+          <t>表12、表15、6.2</t>
         </is>
       </c>
     </row>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>表9所列20家企业的2025年营业收入、归母净利润及同比变动</t>
+          <t>表8所列可比公司的2025年营业收入、归母净利润及同比变动</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>表9、5.1、5.4</t>
+          <t>表8</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>表10</t>
+          <t>表2、表4、表7</t>
         </is>
       </c>
     </row>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>表10、4.1、5.5</t>
+          <t>表2、表4、表7、5.1</t>
         </is>
       </c>
     </row>
@@ -1698,14 +1698,14 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>五家样本企业问询回复中的“中介机构核查程序”章节</t>
+          <t>四家样本企业问询回复中的“中介机构核查程序”章节</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>表13、7.3—7.10</t>
+          <t>表13、6.2—6.7</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>9.1、9.7</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>融资用途为全氟密封圈、金属喷头等关键配件的研发扩产与工艺优化。同篇提及的专利23项、2024年主营收入增速超60%、年产30万套密封组件为单一来源，未获独立印证，本报告正文未采用，列入表18待核实</t>
+          <t>融资用途为全氟密封圈、金属喷头等关键配件的研发扩产与工艺优化。同篇提及的专利23项、2024年主营收入增速超60%、年产30万套密封组件为单一来源，未获独立印证，本报告正文未采用，列入表16待核实</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>9.1、表18</t>
+          <t>1.1、表16</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>表9所列各公司首次公开发行的保荐机构与上市日期。其中正帆科技首次公开发行的保荐机构（主承销商）为国泰君安证券，据其2020年8月7日投资风险特别公告</t>
+          <t>可比公司与国泰海通相关项目的上市日期与保荐机构。其中正帆科技首次公开发行的保荐机构（主承销商）为国泰君安证券，据其2020年8月7日投资风险特别公告</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>表9、表15、8.2</t>
+          <t>表8、表15、7.2</t>
         </is>
       </c>
     </row>
